--- a/assets/templates/cnss_hire_new.xlsx
+++ b/assets/templates/cnss_hire_new.xlsx
@@ -23,7 +23,7 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -37,7 +37,7 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -45,30 +45,14 @@
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
-      <sz val="14"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="13"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="16"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -91,7 +75,23 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="14"/>
+      <sz val="12"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -278,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" readingOrder="2"/>
@@ -510,6 +510,31 @@
       <alignment horizontal="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,7 +927,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>تصريـــح باستـــــخدام أجير</t>
         </is>
@@ -946,9 +971,9 @@
           <t>أ- معلومات خاصة بالمؤسسة :</t>
         </is>
       </c>
-      <c r="I5" s="51" t="n"/>
-      <c r="J5" s="75" t="n"/>
-      <c r="K5" s="75" t="n"/>
+      <c r="I5" s="82" t="n"/>
+      <c r="J5" s="48" t="n"/>
+      <c r="K5" s="48" t="n"/>
       <c r="M5" s="11" t="n"/>
       <c r="P5" s="65" t="inlineStr">
         <is>
@@ -970,7 +995,7 @@
     </row>
     <row r="7" ht="18.9" customHeight="1">
       <c r="A7" s="11" t="n"/>
-      <c r="B7" s="50" t="n"/>
+      <c r="B7" s="83" t="n"/>
       <c r="M7" s="11" t="n"/>
     </row>
     <row r="8" ht="18.9" customHeight="1">
@@ -981,7 +1006,7 @@
         </is>
       </c>
       <c r="K8" s="47" t="n"/>
-      <c r="L8" s="53" t="n"/>
+      <c r="L8" s="84" t="n"/>
       <c r="M8" s="11" t="n"/>
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="2" t="inlineStr">
@@ -999,7 +1024,7 @@
           <t>عنوان المؤسسة(مكان عمل الاجير).</t>
         </is>
       </c>
-      <c r="G9" s="54" t="n"/>
+      <c r="G9" s="47" t="n"/>
       <c r="M9" s="11" t="n"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -1066,15 +1091,15 @@
           <t>اسم الأجير:</t>
         </is>
       </c>
-      <c r="C14" s="54" t="n"/>
-      <c r="D14" s="55" t="n"/>
+      <c r="C14" s="47" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>الشهرة:</t>
         </is>
       </c>
-      <c r="K14" s="54" t="n"/>
-      <c r="L14" s="55" t="n"/>
+      <c r="K14" s="47" t="n"/>
+      <c r="L14" s="2" t="n"/>
       <c r="M14" s="11" t="n"/>
     </row>
     <row r="15" ht="18.9" customHeight="1">
@@ -1086,16 +1111,16 @@
           <t>اسم الأب:</t>
         </is>
       </c>
-      <c r="C15" s="54" t="n"/>
-      <c r="D15" s="55" t="n"/>
+      <c r="C15" s="47" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>.اسم الام وشهرتها</t>
         </is>
       </c>
-      <c r="J15" s="54" t="n"/>
-      <c r="K15" s="55" t="n"/>
-      <c r="L15" s="55" t="n"/>
+      <c r="J15" s="47" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
       <c r="M15" s="11" t="n"/>
       <c r="O15" s="3" t="n"/>
       <c r="P15" s="2" t="inlineStr">
@@ -1113,22 +1138,22 @@
           <t>تاريخ ومحل الولادة:</t>
         </is>
       </c>
-      <c r="D16" s="54" t="n"/>
-      <c r="E16" s="55" t="n"/>
-      <c r="F16" s="55" t="n"/>
+      <c r="D16" s="47" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>القضاء</t>
         </is>
       </c>
-      <c r="I16" s="54" t="n"/>
+      <c r="I16" s="47" t="n"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
           <t>رقم السجل</t>
         </is>
       </c>
-      <c r="L16" s="54" t="n"/>
-      <c r="M16" s="56" t="n"/>
+      <c r="L16" s="47" t="n"/>
+      <c r="M16" s="11" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
           <t>في الصندوق</t>
@@ -1195,16 +1220,16 @@
           <t>محل الاقامة(حسب الهوية)</t>
         </is>
       </c>
-      <c r="E18" s="54" t="n"/>
-      <c r="F18" s="55" t="n"/>
-      <c r="G18" s="55" t="n"/>
+      <c r="E18" s="47" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>المذهب</t>
         </is>
       </c>
-      <c r="J18" s="55" t="n"/>
-      <c r="K18" s="55" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
       <c r="M18" s="11" t="n"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1221,17 +1246,17 @@
           <t>عنوان السكن الحالي: المحافظة:</t>
         </is>
       </c>
-      <c r="E19" s="55" t="n"/>
-      <c r="F19" s="54" t="n"/>
-      <c r="G19" s="55" t="n"/>
-      <c r="H19" s="55" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="47" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
           <t>القضاء</t>
         </is>
       </c>
-      <c r="J19" s="54" t="n"/>
-      <c r="K19" s="55" t="n"/>
+      <c r="J19" s="47" t="n"/>
+      <c r="K19" s="2" t="n"/>
       <c r="M19" s="11" t="n"/>
     </row>
     <row r="20" ht="18.9" customHeight="1">
@@ -1241,24 +1266,24 @@
           <t>المدينة أو القرية</t>
         </is>
       </c>
-      <c r="C20" s="55" t="n"/>
-      <c r="D20" s="54" t="n"/>
-      <c r="E20" s="55" t="n"/>
-      <c r="F20" s="55" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="47" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>الحي</t>
         </is>
       </c>
-      <c r="H20" s="55" t="n"/>
-      <c r="I20" s="54" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="47" t="n"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>الشارع</t>
         </is>
       </c>
-      <c r="K20" s="57" t="n"/>
-      <c r="L20" s="55" t="n"/>
+      <c r="K20" s="85" t="n"/>
+      <c r="L20" s="2" t="n"/>
       <c r="M20" s="11" t="n"/>
     </row>
     <row r="21" ht="18.9" customHeight="1">
@@ -1268,16 +1293,16 @@
           <t>بناية وطابق</t>
         </is>
       </c>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="n"/>
-      <c r="E21" s="55" t="n"/>
+      <c r="C21" s="47" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>هاتف</t>
         </is>
       </c>
-      <c r="I21" s="64" t="n"/>
-      <c r="K21" s="53" t="n"/>
+      <c r="I21" s="81" t="n"/>
+      <c r="K21" s="84" t="n"/>
       <c r="M21" s="11" t="n"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1294,15 +1319,15 @@
           <t>تاريخ دخول العمل</t>
         </is>
       </c>
-      <c r="D22" s="54" t="n"/>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="64" t="n"/>
+      <c r="D22" s="47" t="n"/>
+      <c r="E22" s="47" t="n"/>
+      <c r="F22" s="81" t="n"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>عدد ساعات عمله في الشهر</t>
         </is>
       </c>
-      <c r="L22" s="54" t="n"/>
+      <c r="L22" s="47" t="n"/>
       <c r="M22" s="11" t="n"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1322,7 +1347,7 @@
           <t>كامل</t>
         </is>
       </c>
-      <c r="D23" s="75" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1356,8 +1381,8 @@
           <t>الراتب الحالي :</t>
         </is>
       </c>
-      <c r="J24" s="66" t="n"/>
-      <c r="L24" s="54" t="inlineStr">
+      <c r="J24" s="86" t="n"/>
+      <c r="L24" s="47" t="inlineStr">
         <is>
           <t>ل.ل</t>
         </is>
@@ -1373,7 +1398,7 @@
           <t>الاجر بتاريخ دخول العمل:</t>
         </is>
       </c>
-      <c r="E25" s="54" t="n"/>
+      <c r="E25" s="47" t="n"/>
       <c r="M25" s="11" t="n"/>
     </row>
     <row r="26" ht="18.9" customHeight="1">
@@ -1383,7 +1408,7 @@
           <t>طريقة دفع الأجر: شهري</t>
         </is>
       </c>
-      <c r="D26" s="75" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1518,15 +1543,15 @@
       <c r="E33" s="49" t="n"/>
       <c r="F33" s="49" t="n"/>
       <c r="G33" s="49" t="n"/>
-      <c r="H33" s="58" t="n"/>
+      <c r="H33" s="87" t="n"/>
       <c r="I33" s="49" t="n"/>
       <c r="J33" s="49" t="inlineStr">
         <is>
           <t>التاريخ</t>
         </is>
       </c>
-      <c r="K33" s="67" t="n"/>
-      <c r="L33" s="80" t="n"/>
+      <c r="K33" s="88" t="n"/>
+      <c r="L33" s="89" t="n"/>
       <c r="M33" s="49" t="n"/>
       <c r="N33" s="49" t="n"/>
       <c r="O33" s="49" t="inlineStr">
@@ -1538,6 +1563,7 @@
       <c r="Q33" s="49" t="n"/>
       <c r="R33" s="49" t="n"/>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -1551,8 +1577,9 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="L36" s="64" t="n"/>
-    </row>
+      <c r="L36" s="81" t="n"/>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -1581,28 +1608,28 @@
       <c r="R39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>1- ملاحظة كل صاحب عمل يغفل التصريح عن اجرائه ضمن مهلة(15) يوما من تاريخ الاستخدام أو يتقدم بتصاريخ غير صحيحة يتعرض لعقوبات</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>الغرامة والحبس وذلك عملا بأحكام المادتين 80 و 81 من قانون الضمان الاجتماعي.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>2- يجب أن تطابق المعلومات الواردة أعلاه مع اخراج القيد المرفق(افرادي للأعزب- عائلي للمتأهل)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>3- تنبيه: يهمل كل طلب غير مكتوب بخط واضح ومقروء ومعلومات ناقصة.</t>
         </is>

--- a/assets/templates/cnss_hire_new.xlsx
+++ b/assets/templates/cnss_hire_new.xlsx
@@ -276,7 +276,7 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -926,21 +926,21 @@
     <col width="9.109375" customWidth="1" style="2" min="21" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="20.7" customHeight="1">
       <c r="A1" s="81" t="inlineStr">
         <is>
           <t>تصريـــح باستـــــخدام أجير</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="17.9" customHeight="1">
       <c r="A2" s="65" t="inlineStr">
         <is>
           <t>(يملأ هذا التصريح من قبل صاحب العمل وعلى مسؤوليته)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="8.1" customHeight="1" thickBot="1">
+    <row r="3" ht="9.300000000000001" customHeight="1" thickBot="1">
       <c r="A3" s="7" t="n"/>
       <c r="B3" s="7" t="n"/>
       <c r="C3" s="7" t="n"/>
@@ -960,11 +960,11 @@
       <c r="Q3" s="7" t="n"/>
       <c r="R3" s="6" t="n"/>
     </row>
-    <row r="4" ht="8.1" customHeight="1">
+    <row r="4" ht="9.300000000000001" customHeight="1">
       <c r="A4" s="11" t="n"/>
       <c r="M4" s="11" t="n"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1">
+    <row r="5" ht="23.1" customHeight="1">
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="Q5" s="65" t="n"/>
     </row>
-    <row r="6" ht="18.9" customHeight="1">
+    <row r="6" ht="21.7" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>1</v>
       </c>
@@ -993,12 +993,12 @@
       </c>
       <c r="M6" s="11" t="n"/>
     </row>
-    <row r="7" ht="18.9" customHeight="1">
+    <row r="7" ht="21.7" customHeight="1">
       <c r="A7" s="11" t="n"/>
       <c r="B7" s="83" t="n"/>
       <c r="M7" s="11" t="n"/>
     </row>
-    <row r="8" ht="18.9" customHeight="1">
+    <row r="8" ht="21.7" customHeight="1">
       <c r="A8" s="13" t="n"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18.9" customHeight="1">
+    <row r="9" ht="21.7" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>2</v>
       </c>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18.9" customHeight="1">
+    <row r="10" ht="21.7" customHeight="1">
       <c r="A10" s="11" t="n"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -1043,11 +1043,11 @@
       <c r="P10" s="9" t="n"/>
       <c r="Q10" s="3" t="n"/>
     </row>
-    <row r="11" ht="18.9" customHeight="1">
+    <row r="11" ht="21.7" customHeight="1">
       <c r="A11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
     </row>
-    <row r="12" ht="18.9" customHeight="1">
+    <row r="12" ht="21.7" customHeight="1">
       <c r="A12" s="11" t="n"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="M12" s="11" t="n"/>
     </row>
-    <row r="13" ht="18.9" customHeight="1">
+    <row r="13" ht="21.7" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>3</v>
       </c>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="M13" s="11" t="n"/>
     </row>
-    <row r="14" ht="18.9" customHeight="1">
+    <row r="14" ht="21.7" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>4</v>
       </c>
@@ -1102,7 +1102,7 @@
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="11" t="n"/>
     </row>
-    <row r="15" ht="18.9" customHeight="1">
+    <row r="15" ht="21.7" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>5</v>
       </c>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18.9" customHeight="1">
+    <row r="16" ht="21.7" customHeight="1">
       <c r="A16" s="11" t="n">
         <v>6</v>
       </c>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18.9" customHeight="1">
+    <row r="17" ht="21.7" customHeight="1">
       <c r="A17" s="11" t="n">
         <v>7</v>
       </c>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18.9" customHeight="1">
+    <row r="18" ht="21.7" customHeight="1">
       <c r="A18" s="11" t="n">
         <v>8</v>
       </c>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18.9" customHeight="1">
+    <row r="19" ht="21.7" customHeight="1">
       <c r="A19" s="11" t="n">
         <v>9</v>
       </c>
@@ -1259,7 +1259,7 @@
       <c r="K19" s="2" t="n"/>
       <c r="M19" s="11" t="n"/>
     </row>
-    <row r="20" ht="18.9" customHeight="1">
+    <row r="20" ht="21.7" customHeight="1">
       <c r="A20" s="11" t="n"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="11" t="n"/>
     </row>
-    <row r="21" ht="18.9" customHeight="1">
+    <row r="21" ht="21.7" customHeight="1">
       <c r="A21" s="11" t="n"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18.9" customHeight="1">
+    <row r="22" ht="21.7" customHeight="1">
       <c r="A22" s="11" t="n">
         <v>10</v>
       </c>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="18.9" customHeight="1">
+    <row r="23" ht="21.7" customHeight="1">
       <c r="A23" s="11" t="n"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
       <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="n"/>
     </row>
-    <row r="24" ht="18.9" customHeight="1">
+    <row r="24" ht="21.7" customHeight="1">
       <c r="A24" s="11" t="n">
         <v>11</v>
       </c>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M24" s="11" t="n"/>
     </row>
-    <row r="25" ht="18.9" customHeight="1">
+    <row r="25" ht="21.7" customHeight="1">
       <c r="A25" s="11" t="n">
         <v>12</v>
       </c>
@@ -1401,7 +1401,7 @@
       <c r="E25" s="47" t="n"/>
       <c r="M25" s="11" t="n"/>
     </row>
-    <row r="26" ht="18.9" customHeight="1">
+    <row r="26" ht="21.7" customHeight="1">
       <c r="A26" s="11" t="n"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="18.9" customHeight="1">
+    <row r="27" ht="21.7" customHeight="1">
       <c r="A27" s="11" t="n">
         <v>13</v>
       </c>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="18.9" customHeight="1">
+    <row r="28" ht="21.7" customHeight="1">
       <c r="A28" s="11" t="n"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="M28" s="11" t="n"/>
     </row>
-    <row r="29" ht="18.9" customHeight="1">
+    <row r="29" ht="21.7" customHeight="1">
       <c r="A29" s="11" t="n">
         <v>14</v>
       </c>
@@ -1504,11 +1504,11 @@
       </c>
       <c r="M29" s="11" t="n"/>
     </row>
-    <row r="30" ht="18.9" customHeight="1">
+    <row r="30" ht="21.7" customHeight="1">
       <c r="A30" s="11" t="n"/>
       <c r="M30" s="11" t="n"/>
     </row>
-    <row r="31" ht="20.1" customHeight="1">
+    <row r="31" ht="23.1" customHeight="1">
       <c r="A31" s="11" t="n">
         <v>15</v>
       </c>
@@ -1527,11 +1527,11 @@
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="11" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
+    <row r="32" ht="20.7" customHeight="1">
       <c r="A32" s="11" t="n"/>
       <c r="M32" s="11" t="n"/>
     </row>
-    <row r="33" ht="21.9" customHeight="1" thickBot="1">
+    <row r="33" ht="25.2" customHeight="1" thickBot="1">
       <c r="A33" s="49" t="inlineStr">
         <is>
           <t>اوافق على صحة المعلومات المدرجة أعلاه: اسم الأجير:</t>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="K33" s="88" t="n"/>
-      <c r="L33" s="89" t="n"/>
+      <c r="L33" s="80" t="n"/>
       <c r="M33" s="49" t="n"/>
       <c r="N33" s="49" t="n"/>
       <c r="O33" s="49" t="inlineStr">
@@ -1563,8 +1563,8 @@
       <c r="Q33" s="49" t="n"/>
       <c r="R33" s="49" t="n"/>
     </row>
-    <row r="34"/>
-    <row r="35">
+    <row r="34" ht="17.9" customHeight="1"/>
+    <row r="35" ht="17.9" customHeight="1">
       <c r="I35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ختم المؤسسة                 </t>
@@ -1576,18 +1576,18 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
+    <row r="36" ht="20.7" customHeight="1">
       <c r="L36" s="81" t="n"/>
     </row>
-    <row r="37"/>
-    <row r="38">
+    <row r="37" ht="17.9" customHeight="1"/>
+    <row r="38" ht="17.9" customHeight="1">
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>...................في...........................</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="10.8" customHeight="1" thickBot="1">
+    <row r="39" ht="12.4" customHeight="1" thickBot="1">
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="6" t="n"/>
@@ -1607,28 +1607,28 @@
       <c r="Q39" s="6" t="n"/>
       <c r="R39" s="6" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="17.9" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>1- ملاحظة كل صاحب عمل يغفل التصريح عن اجرائه ضمن مهلة(15) يوما من تاريخ الاستخدام أو يتقدم بتصاريخ غير صحيحة يتعرض لعقوبات</t>
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="17.9" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>الغرامة والحبس وذلك عملا بأحكام المادتين 80 و 81 من قانون الضمان الاجتماعي.</t>
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="17.9" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>2- يجب أن تطابق المعلومات الواردة أعلاه مع اخراج القيد المرفق(افرادي للأعزب- عائلي للمتأهل)</t>
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="17.9" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>3- تنبيه: يهمل كل طلب غير مكتوب بخط واضح ومقروء ومعلومات ناقصة.</t>
